--- a/data/trans_camb/P45C_R1-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R1-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,87</t>
+          <t>0,39; 2,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,44</t>
+          <t>-0,34; 1,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,69</t>
+          <t>-0,24; 1,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,24</t>
+          <t>0,94; 3,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,03</t>
+          <t>0,27; 1,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,1</t>
+          <t>0,9; 2,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,76</t>
+          <t>0,94; 2,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,41</t>
+          <t>0,2; 1,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,1</t>
+          <t>0,51; 1,97</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 17178755,32</t>
+          <t>-30,12; 21303241,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-86,7; 11741273,77</t>
+          <t>-78,5; 14768997,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-85,26; 8530676,42</t>
+          <t>-69,74; 17637900,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>110,41; 3191,01</t>
+          <t>72,22; 2833,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 1675,75</t>
+          <t>-12,5; 1323,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41,05; 2322,99</t>
+          <t>19,11; 2222,01</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,05</t>
+          <t>-1,25; 1,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,14</t>
+          <t>-1,74; 0,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,41</t>
+          <t>-1,3; 1,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,1</t>
+          <t>-1,11; 0,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,83</t>
+          <t>-1,4; 0,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,18</t>
+          <t>-0,99; 1,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,77</t>
+          <t>-0,94; 0,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,21</t>
+          <t>-1,26; 0,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,99</t>
+          <t>-0,74; 0,97</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-61,79; 121,37</t>
+          <t>-62,42; 124,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-85,73; 24,46</t>
+          <t>-85,2; 37,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-59,56; 154,76</t>
+          <t>-63,88; 141,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-56,34; 120,18</t>
+          <t>-54,54; 109,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,46; 81,58</t>
+          <t>-65,75; 93,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,82; 122,75</t>
+          <t>-49,21; 134,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,55; 71,9</t>
+          <t>-46,79; 58,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,67; 25,4</t>
+          <t>-63,53; 18,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-39,89; 85,41</t>
+          <t>-42,29; 81,8</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,07</t>
+          <t>-3,24; -0,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 0,58</t>
+          <t>-2,89; 0,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,41</t>
+          <t>-2,38; 1,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,25; -0,51</t>
+          <t>-3,07; -0,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 0,16</t>
+          <t>-2,7; 0,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,79</t>
+          <t>-2,66; 0,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; -0,57</t>
+          <t>-2,68; -0,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; -0,1</t>
+          <t>-2,36; -0,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,47</t>
+          <t>-2,11; 0,45</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-80,53; 6,22</t>
+          <t>-79,94; 5,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-77,5; 41,62</t>
+          <t>-76,38; 24,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-68,82; 93,94</t>
+          <t>-64,96; 69,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-89,71; -17,1</t>
+          <t>-89,11; -20,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,84; 23,12</t>
+          <t>-78,79; 12,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,4; 43,28</t>
+          <t>-73,6; 41,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-79,62; -25,0</t>
+          <t>-78,61; -27,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,72; -1,72</t>
+          <t>-68,41; -3,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-59,41; 25,87</t>
+          <t>-62,92; 20,67</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,68; -0,36</t>
+          <t>-2,46; -0,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; -0,62</t>
+          <t>-2,62; -0,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1340,32 +1340,32 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,99</t>
+          <t>-1,47; 1,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,48; -0,26</t>
+          <t>-2,46; -0,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,67; -0,78</t>
+          <t>-2,72; -0,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,05</t>
+          <t>-1,69; 0,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; -0,69</t>
+          <t>-2,26; -0,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; -0,25</t>
+          <t>-1,92; -0,3</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-91,16; -19,03</t>
+          <t>-89,11; -24,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-91,25; -32,24</t>
+          <t>-89,54; -21,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,86; 58,44</t>
+          <t>-60,62; 62,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-53,0; 68,07</t>
+          <t>-50,29; 71,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-83,93; -11,82</t>
+          <t>-82,91; -19,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-88,46; -43,0</t>
+          <t>-89,09; -40,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-61,15; 7,29</t>
+          <t>-61,57; 7,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-82,23; -37,44</t>
+          <t>-80,23; -35,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-70,07; -4,03</t>
+          <t>-69,73; -15,08</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,16</t>
+          <t>-1,06; 0,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,37; -0,21</t>
+          <t>-1,38; -0,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,55</t>
+          <t>-0,81; 0,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,55</t>
+          <t>-0,72; 0,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,04</t>
+          <t>-1,12; 0,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,31</t>
+          <t>-0,9; 0,34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,19</t>
+          <t>-0,7; 0,23</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,07; -0,28</t>
+          <t>-1,1; -0,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,32</t>
+          <t>-0,65; 0,28</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-49,18; 13,58</t>
+          <t>-50,24; 13,51</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-66,82; -12,07</t>
+          <t>-66,36; -11,82</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-40,09; 41,18</t>
+          <t>-41,27; 49,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 38,2</t>
+          <t>-35,26; 39,83</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-54,64; 3,5</t>
+          <t>-55,31; 4,55</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-43,02; 24,5</t>
+          <t>-44,33; 25,12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-34,99; 13,59</t>
+          <t>-35,53; 15,77</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-55,98; -18,82</t>
+          <t>-55,61; -17,9</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-30,69; 21,06</t>
+          <t>-34,67; 19,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P45C_R1-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R1-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,75</t>
+          <t>1,59</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,09</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,85</t>
+          <t>0,51; 2,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,49</t>
+          <t>-0,32; 1,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,81</t>
+          <t>-0,36; 1,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,29</t>
+          <t>0,95; 3,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,9</t>
+          <t>0,24; 1,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,99</t>
+          <t>0,77; 2,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,57</t>
+          <t>0,99; 2,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,41</t>
+          <t>0,18; 1,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,97</t>
+          <t>0,42; 1,79</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>154,87%</t>
+          <t>137,89%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1245,4%</t>
+          <t>1135,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>437,97%</t>
+          <t>396,57%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,12; 21303241,4</t>
+          <t>-33,93; 17225318,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-78,5; 14768997,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-69,74; 17637900,81</t>
+          <t>-88,58; 10328828,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,22; 2833,53</t>
+          <t>85,45; 2914,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 1323,48</t>
+          <t>-1,11; 1478,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,11; 2222,01</t>
+          <t>31,77; 1948,66</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,25</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,02</t>
+          <t>-1,13; 1,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,23</t>
+          <t>-1,75; 0,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,41</t>
+          <t>-0,74; 1,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,97</t>
+          <t>-1,07; 1,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,83</t>
+          <t>-1,48; 0,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,22</t>
+          <t>-1,06; 1,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,66</t>
+          <t>-0,77; 0,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,19</t>
+          <t>-1,22; 0,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,97</t>
+          <t>-0,55; 1,15</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-62,42; 124,82</t>
+          <t>-59,79; 117,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-85,2; 37,88</t>
+          <t>-84,7; 29,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,88; 141,06</t>
+          <t>-41,51; 204,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-54,54; 109,19</t>
+          <t>-54,11; 110,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,75; 93,41</t>
+          <t>-65,76; 79,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,21; 134,85</t>
+          <t>-47,75; 143,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,79; 58,95</t>
+          <t>-42,59; 69,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,53; 18,22</t>
+          <t>-65,85; 23,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,29; 81,8</t>
+          <t>-30,54; 108,37</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>-0,31</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; -0,02</t>
+          <t>-3,11; -0,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 0,45</t>
+          <t>-3,0; 0,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 1,29</t>
+          <t>-2,45; 1,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; -0,53</t>
+          <t>-3,32; -0,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 0,18</t>
+          <t>-2,79; 0,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,66</t>
+          <t>-1,74; 1,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,68; -0,58</t>
+          <t>-2,73; -0,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; -0,18</t>
+          <t>-2,37; -0,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,45</t>
+          <t>-1,68; 0,8</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-23,04%</t>
+          <t>-19,19%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-31,15%</t>
+          <t>-3,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-27,92%</t>
+          <t>-11,75%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-79,94; 5,8</t>
+          <t>-79,53; 3,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,38; 24,52</t>
+          <t>-77,04; 32,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-64,96; 69,92</t>
+          <t>-65,42; 79,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-89,11; -20,14</t>
+          <t>-91,59; -25,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-78,79; 12,49</t>
+          <t>-78,56; 14,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,6; 41,97</t>
+          <t>-49,71; 107,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-78,61; -27,21</t>
+          <t>-78,23; -25,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,41; -3,11</t>
+          <t>-70,15; -3,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,92; 20,67</t>
+          <t>-48,77; 40,38</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-0,46</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,62</t>
+          <t>-1,57</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,06</t>
+          <t>-1,05</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; -0,42</t>
+          <t>-2,55; -0,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; -0,54</t>
+          <t>-2,61; -0,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,81</t>
+          <t>-1,74; 0,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,08</t>
+          <t>-1,56; 1,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; -0,36</t>
+          <t>-2,55; -0,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; -0,75</t>
+          <t>-2,8; -0,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,1</t>
+          <t>-1,61; 0,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; -0,69</t>
+          <t>-2,19; -0,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,92; -0,3</t>
+          <t>-1,82; -0,29</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-18,97%</t>
+          <t>-22,38%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-73,11%</t>
+          <t>-70,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-49,13%</t>
+          <t>-48,86%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-89,11; -24,3</t>
+          <t>-86,41; -14,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-89,54; -21,82</t>
+          <t>-89,25; -26,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,62; 62,95</t>
+          <t>-62,1; 74,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,29; 71,2</t>
+          <t>-50,93; 65,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-82,91; -19,36</t>
+          <t>-84,27; -15,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-89,09; -40,05</t>
+          <t>-88,02; -38,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-61,57; 7,7</t>
+          <t>-60,81; 4,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-80,23; -35,15</t>
+          <t>-82,01; -42,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-69,73; -15,08</t>
+          <t>-66,85; -12,92</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,06</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,15</t>
+          <t>-1,03; 0,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,38; -0,22</t>
+          <t>-1,44; -0,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,66</t>
+          <t>-0,65; 0,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,55</t>
+          <t>-0,7; 0,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,01</t>
+          <t>-1,06; 0,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,34</t>
+          <t>-0,66; 0,5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,23</t>
+          <t>-0,67; 0,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; -0,28</t>
+          <t>-1,08; -0,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,28</t>
+          <t>-0,47; 0,4</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-15,48%</t>
+          <t>-7,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-10,41%</t>
+          <t>-3,45%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-50,24; 13,51</t>
+          <t>-50,63; 19,67</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-66,36; -11,82</t>
+          <t>-68,28; -11,51</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,27; 49,01</t>
+          <t>-33,46; 54,08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-35,26; 39,83</t>
+          <t>-34,88; 40,05</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-55,31; 4,55</t>
+          <t>-54,82; 3,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-44,33; 25,12</t>
+          <t>-33,96; 36,95</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-35,53; 15,77</t>
+          <t>-34,16; 15,21</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-55,61; -17,9</t>
+          <t>-55,67; -18,33</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-34,67; 19,26</t>
+          <t>-25,13; 28,54</t>
         </is>
       </c>
     </row>
